--- a/stim/stim_group_lists_training.xlsx
+++ b/stim/stim_group_lists_training.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24701"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\speechres\Task_SpeechMotorSequenceLearning\stim\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\amsme\OneDrive\Documents\code\matlab\Task_SpeechMotorSequenceLearning\stim\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4F0B31E-D141-4CA6-BBFB-E53ADFFE177A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F02EDC2-8D2F-4560-9712-3E1994245D76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,9 +21,6 @@
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="18">
-  <si>
-    <t>native</t>
-  </si>
   <si>
     <t>group1</t>
   </si>
@@ -49,9 +46,6 @@
     <t>stop_trial</t>
   </si>
   <si>
-    <t>STOP (native)</t>
-  </si>
-  <si>
     <t>non-native learned</t>
   </si>
   <si>
@@ -74,6 +68,12 @@
   </si>
   <si>
     <t>group7</t>
+  </si>
+  <si>
+    <t>native learned</t>
+  </si>
+  <si>
+    <t>STOP (native learned)</t>
   </si>
 </sst>
 </file>
@@ -439,41 +439,41 @@
   <cols>
     <col min="1" max="5" width="11.5703125" style="1"/>
     <col min="6" max="7" width="11.5703125" style="4"/>
-    <col min="8" max="8" width="18.28515625" customWidth="1"/>
+    <col min="8" max="8" width="19.42578125" customWidth="1"/>
     <col min="9" max="9" width="8.5703125" style="3" customWidth="1"/>
     <col min="10" max="10" width="8.28515625" style="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="3" t="s">
         <v>7</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
@@ -499,7 +499,7 @@
         <v>13</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I2" s="3">
         <v>1</v>
@@ -531,7 +531,7 @@
         <v>13</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I3" s="3">
         <v>1</v>
@@ -563,7 +563,7 @@
         <v>13</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I4" s="3">
         <v>1</v>
@@ -595,7 +595,7 @@
         <v>13</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I5" s="3">
         <v>1</v>
@@ -627,7 +627,7 @@
         <v>13</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I6" s="3">
         <v>1</v>
@@ -659,7 +659,7 @@
         <v>13</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I7" s="3">
         <v>1</v>
@@ -691,7 +691,7 @@
         <v>13</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I8" s="3">
         <v>1</v>
@@ -723,7 +723,7 @@
         <v>13</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I9" s="3">
         <v>1</v>
@@ -755,7 +755,7 @@
         <v>13</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I10" s="3">
         <v>1</v>
@@ -787,7 +787,7 @@
         <v>13</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I11" s="3">
         <v>1</v>
@@ -819,7 +819,7 @@
         <v>13</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I12" s="3">
         <v>1</v>
@@ -851,7 +851,7 @@
         <v>13</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I13" s="3">
         <v>1</v>
@@ -883,7 +883,7 @@
         <v>14</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I14" s="3">
         <v>1</v>
@@ -915,7 +915,7 @@
         <v>14</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I15" s="3">
         <v>1</v>
@@ -947,7 +947,7 @@
         <v>14</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I16" s="3">
         <v>1</v>
@@ -979,7 +979,7 @@
         <v>14</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I17" s="3">
         <v>1</v>
@@ -1011,7 +1011,7 @@
         <v>14</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I18" s="3">
         <v>1</v>
@@ -1043,7 +1043,7 @@
         <v>14</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I19" s="3">
         <v>1</v>
@@ -1075,7 +1075,7 @@
         <v>14</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I20" s="3">
         <v>1</v>
@@ -1107,7 +1107,7 @@
         <v>14</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I21" s="3">
         <v>1</v>
@@ -1139,7 +1139,7 @@
         <v>14</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I22" s="3">
         <v>1</v>
@@ -1171,7 +1171,7 @@
         <v>14</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I23" s="3">
         <v>1</v>
@@ -1203,7 +1203,7 @@
         <v>14</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I24" s="3">
         <v>1</v>
@@ -1235,7 +1235,7 @@
         <v>14</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I25" s="3">
         <v>1</v>
@@ -1267,7 +1267,7 @@
         <v>25</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="I26" s="3">
         <v>3</v>
@@ -1299,7 +1299,7 @@
         <v>26</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="I27" s="3">
         <v>3</v>
@@ -1331,7 +1331,7 @@
         <v>27</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="I28" s="3">
         <v>3</v>
@@ -1363,7 +1363,7 @@
         <v>28</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="I29" s="3">
         <v>3</v>
@@ -1395,7 +1395,7 @@
         <v>29</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="I30" s="3">
         <v>3</v>
@@ -1427,7 +1427,7 @@
         <v>30</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="I31" s="3">
         <v>3</v>
@@ -1459,7 +1459,7 @@
         <v>31</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="I32" s="3">
         <v>3</v>
@@ -1491,7 +1491,7 @@
         <v>32</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="I33" s="3">
         <v>3</v>
@@ -1523,7 +1523,7 @@
         <v>33</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="I34" s="3">
         <v>3</v>
@@ -1555,7 +1555,7 @@
         <v>34</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="I35" s="3">
         <v>3</v>
@@ -1587,7 +1587,7 @@
         <v>35</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="I36" s="3">
         <v>3</v>
@@ -1619,7 +1619,7 @@
         <v>36</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="I37" s="3">
         <v>3</v>
@@ -1651,7 +1651,7 @@
         <v>13</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I38" s="3">
         <v>1</v>
@@ -1683,7 +1683,7 @@
         <v>13</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I39" s="3">
         <v>1</v>
@@ -1715,7 +1715,7 @@
         <v>13</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I40" s="3">
         <v>1</v>
@@ -1747,7 +1747,7 @@
         <v>13</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I41" s="3">
         <v>1</v>
@@ -1779,7 +1779,7 @@
         <v>14</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I42" s="3">
         <v>1</v>
@@ -1811,7 +1811,7 @@
         <v>14</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I43" s="3">
         <v>1</v>
@@ -1843,7 +1843,7 @@
         <v>14</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I44" s="3">
         <v>1</v>
@@ -1875,7 +1875,7 @@
         <v>14</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I45" s="3">
         <v>1</v>
@@ -1886,28 +1886,28 @@
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A46" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="I46" s="3">
         <v>3</v>
@@ -1918,28 +1918,28 @@
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A47" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="I47" s="3">
         <v>3</v>
@@ -1950,28 +1950,28 @@
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A48" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G48" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="I48" s="3">
         <v>3</v>
@@ -1982,28 +1982,28 @@
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A49" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="I49" s="3">
         <v>3</v>
